--- a/火山引擎报价单-北京-云服务器4c8g-5M.xlsx
+++ b/火山引擎报价单-北京-云服务器4c8g-5M.xlsx
@@ -1568,17 +1568,14 @@
         </is>
       </c>
       <c r="E4" s="22">
-        <f>3848.2+1167.8</f>
+        <f>3328.08+1687.92</f>
+        <v>5016</v>
         <v/>
       </c>
       <c r="F4" s="22" t="n">
-        <v>3848.2</v>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>实例：ecs.c4i.xlarge 包1年刊例价4176元/年；系统盘40G、数据盘100G 均按极速型SSD PL0 0.5元/GiB/月</t>
-        </is>
-      </c>
+        <v>3328.08</v>
+      </c>
+      <c r="G4" s="10" t="n"/>
     </row>
     <row r="5" ht="61.5" customHeight="1" s="19">
       <c r="A5" s="6" t="n">
@@ -1603,16 +1600,13 @@
       </c>
       <c r="E5" s="22">
         <f>1234.2+217.8</f>
+        <v>1452</v>
         <v/>
       </c>
       <c r="F5" s="22" t="n">
         <v>1234.2</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>带宽费=[1~2M单价23元/月/Mbps×2 + 3~5M单价25元/月/Mbps×3]×12月=1452元/年</t>
-        </is>
-      </c>
+      <c r="G5" s="10" t="n"/>
     </row>
     <row r="6" ht="35" customHeight="1" s="19">
       <c r="A6" s="23" t="inlineStr">
@@ -1625,10 +1619,12 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="24">
         <f>SUM(E4:E5)</f>
+        <v>6468</v>
         <v/>
       </c>
       <c r="F6" s="25">
         <f>SUM(F4:F5)</f>
+        <v>4562.28</v>
         <v/>
       </c>
       <c r="G6" s="17" t="inlineStr">

--- a/火山引擎报价单-北京-云服务器4c8g-5M.xlsx
+++ b/火山引擎报价单-北京-云服务器4c8g-5M.xlsx
@@ -1161,58 +1161,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1463,7 +1411,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1560,16 +1508,13 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>实例规格：ecs.c4i.xlarge
-（计算型 c4i   4 vCPU | 8 GiB）
-系统盘：极速型SSD PL0  40GB
-数据盘：极速型SSD PL0  100GB
-数量：1台</t>
+          <t>实例规格：ecs.c4i.xlarge（4vCPU/8GiB）
+系统盘：极速型SSD PL0  40G
+数据盘：极速型SSD PL0  100G</t>
         </is>
       </c>
       <c r="E4" s="22">
         <f>3328.08+1687.92</f>
-        <v>5016</v>
         <v/>
       </c>
       <c r="F4" s="22" t="n">
@@ -1591,16 +1536,14 @@
           <t>北京</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>线路类型：BGP多线
-带宽大小：5M
-数量：1台</t>
+带宽大小：5M</t>
         </is>
       </c>
       <c r="E5" s="22">
         <f>1234.2+217.8</f>
-        <v>1452</v>
         <v/>
       </c>
       <c r="F5" s="22" t="n">
@@ -1619,12 +1562,10 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="24">
         <f>SUM(E4:E5)</f>
-        <v>6468</v>
         <v/>
       </c>
       <c r="F6" s="25">
         <f>SUM(F4:F5)</f>
-        <v>4562.28</v>
         <v/>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -1633,21 +1574,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="76.5" customHeight="1" s="19"/>
-    <row r="8" ht="76.5" customHeight="1" s="19"/>
-    <row r="9" ht="61.5" customHeight="1" s="19"/>
-    <row r="10" ht="31.5" customHeight="1" s="19"/>
-    <row r="11" ht="31.5" customHeight="1" s="19"/>
-    <row r="12" ht="31.5" customHeight="1" s="19"/>
-    <row r="13" ht="31.5" customHeight="1" s="19"/>
-    <row r="14" ht="35" customHeight="1" s="19"/>
-    <row r="15" ht="14.85" customHeight="1" s="19"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/火山引擎报价单-北京-云服务器4c8g-5M.xlsx
+++ b/火山引擎报价单-北京-云服务器4c8g-5M.xlsx
@@ -1163,6 +1163,58 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1411,7 +1463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1580,5 +1632,6 @@
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>